--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_2_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_2_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268974.3716841202</v>
+        <v>289525.0943648088</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928672</v>
+        <v>4919887.017322725</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22242013.24433631</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042825.87678395</v>
+        <v>4064479.873020301</v>
       </c>
     </row>
     <row r="11">
@@ -1882,16 +1882,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>14.57032318233809</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>14.57032318233809</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>14.57032318233809</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2077,16 +2077,16 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="21">
@@ -2147,16 +2147,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2207,16 +2207,16 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
     </row>
     <row r="22">
@@ -2226,25 +2226,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9.137025436486057</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.790450447682255</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2289,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2365,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
     </row>
     <row r="24">
@@ -2384,25 +2384,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2441,10 +2441,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2466,19 +2466,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.7904504476822691</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="26">
@@ -2545,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2599,19 +2599,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2681,16 +2681,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2715,13 +2715,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2760,16 +2760,16 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="30">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2873,13 +2873,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2912,19 +2912,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X30" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2997,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>40</v>
+        <v>0.7904504476822691</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="32">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="33">
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>35.23199999999997</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>38.12502610536669</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3192,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>24.14609287549672</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="35">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>28.88091821707973</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="36">
@@ -3335,19 +3335,19 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>38.12502610536669</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3398,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3465,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>42.20118209180436</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y38" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="40">
@@ -3651,10 +3651,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3690,34 +3690,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.415584701379575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3733,16 +3733,16 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>35.23199999999997</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3781,22 +3781,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3863,19 +3863,19 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X42" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="43">
@@ -3927,34 +3927,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>6.415584701379575</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
     </row>
     <row r="44">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>17.70009741723633</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>34.07682306495965</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>49.79186282792648</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>49.79186282792648</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>51.45109031167195</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>34.74185079761897</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.03261128356598</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>17.70009741723633</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>33.41513718020315</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>33.41513718020315</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>33.41513718020315</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>33.41513718020315</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>49.79186282792648</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>49.45934896159683</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>16.04086993349086</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.04086993349086</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.323371769512996</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>17.70009741723633</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>34.07682306495965</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>49.79186282792648</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>66.16858847564981</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>49.45934896159683</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>32.75010944754385</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E20" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G20" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K20" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L20" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M20" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N20" t="n">
-        <v>80.80000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O20" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W20" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X20" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y20" t="n">
-        <v>160</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C21" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D21" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K21" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L21" t="n">
-        <v>82.40000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M21" t="n">
-        <v>120.4</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N21" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O21" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P21" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V21" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W21" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X21" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y21" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C22" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D22" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E22" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F22" t="n">
-        <v>29.55856016516557</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G22" t="n">
-        <v>29.55856016516557</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H22" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="I22" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="J22" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="K22" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="L22" t="n">
-        <v>56.87268517287855</v>
+        <v>69.3105240343566</v>
       </c>
       <c r="M22" t="n">
-        <v>96.06072336510073</v>
+        <v>108.4985622265788</v>
       </c>
       <c r="N22" t="n">
-        <v>135.6607233651007</v>
+        <v>152.1894128820151</v>
       </c>
       <c r="O22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V22" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W22" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X22" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y22" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C23" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D23" t="n">
-        <v>124.4121212121212</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E23" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K23" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L23" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M23" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N23" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O23" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V23" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W23" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X23" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y23" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C24" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D24" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K24" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L24" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M24" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N24" t="n">
-        <v>80.80000000000001</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="O24" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="P24" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U24" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>84.00808080808082</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C25" t="n">
-        <v>43.60404040404041</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S25" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T25" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U25" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V25" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W25" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="X25" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Y25" t="n">
-        <v>84.00808080808082</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K26" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L26" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M26" t="n">
-        <v>122</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N26" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O26" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U26" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V26" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="W26" t="n">
-        <v>119.5959595959596</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="X26" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y26" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C27" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L27" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M27" t="n">
-        <v>82.40000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N27" t="n">
-        <v>82.40000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O27" t="n">
-        <v>122</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="T27" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U27" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V27" t="n">
-        <v>160</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="W27" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X27" t="n">
-        <v>160</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y27" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L28" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M28" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N28" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V28" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="W28" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X28" t="n">
-        <v>52.83335902675362</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="Y28" t="n">
-        <v>12.42931862271321</v>
+        <v>48.90696048418764</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D29" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E29" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K29" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="L29" t="n">
-        <v>82.40000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M29" t="n">
-        <v>120.4</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="N29" t="n">
-        <v>120.4</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V29" t="n">
-        <v>149.9083846317729</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W29" t="n">
-        <v>149.9083846317729</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="X29" t="n">
-        <v>109.5043442277325</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="Y29" t="n">
-        <v>69.10030382369209</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D30" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L30" t="n">
-        <v>41.20000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M30" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N30" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O30" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T30" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U30" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V30" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W30" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X30" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y30" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q31" t="n">
-        <v>124.4121212121212</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R31" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S31" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T31" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U31" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V31" t="n">
-        <v>43.60404040404041</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W31" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X31" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>109.5043442277325</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C32" t="n">
-        <v>109.5043442277325</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D32" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E32" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K32" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L32" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M32" t="n">
-        <v>80.80000000000001</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="N32" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q32" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R32" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S32" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T32" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U32" t="n">
-        <v>109.5043442277325</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V32" t="n">
-        <v>109.5043442277325</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W32" t="n">
-        <v>109.5043442277325</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X32" t="n">
-        <v>109.5043442277325</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y32" t="n">
-        <v>109.5043442277325</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="C33" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D33" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F33" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G33" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L33" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M33" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N33" t="n">
-        <v>120.4</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O33" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P33" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W33" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X33" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y33" t="n">
-        <v>38.78787878787876</v>
+        <v>176.5286895169144</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H34" t="n">
-        <v>90.48846939533291</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I34" t="n">
-        <v>50.0844289912925</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J34" t="n">
-        <v>25.69443618776046</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L34" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M34" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N34" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O34" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P34" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q34" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R34" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S34" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T34" t="n">
-        <v>130.8925097993733</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="U34" t="n">
-        <v>130.8925097993733</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="V34" t="n">
-        <v>130.8925097993733</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="W34" t="n">
-        <v>130.8925097993733</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X34" t="n">
-        <v>130.8925097993733</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y34" t="n">
-        <v>130.8925097993733</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="C35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="D35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K35" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L35" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M35" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N35" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="U35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="V35" t="n">
-        <v>119.5959595959596</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="W35" t="n">
-        <v>119.5959595959596</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="X35" t="n">
-        <v>79.19191919191917</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="Y35" t="n">
-        <v>38.78787878787876</v>
+        <v>32.70321845405519</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="C36" t="n">
-        <v>38.78787878787876</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K36" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L36" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M36" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O36" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X36" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y36" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C37" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P37" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="R37" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="S37" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="T37" t="n">
-        <v>133.6414398348344</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U37" t="n">
-        <v>133.6414398348344</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="V37" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W37" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X37" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y37" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C38" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D38" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L38" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M38" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N38" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S38" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="T38" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="U38" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="V38" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W38" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="X38" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y38" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L39" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M39" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N39" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O39" t="n">
-        <v>120.4</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R39" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S39" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T39" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="U39" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V39" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W39" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X39" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C40" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="D40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="E40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="F40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P40" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q40" t="n">
-        <v>130.8925097993733</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R40" t="n">
-        <v>90.48846939533291</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S40" t="n">
-        <v>50.0844289912925</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T40" t="n">
-        <v>50.0844289912925</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U40" t="n">
-        <v>9.680388587252096</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V40" t="n">
-        <v>9.680388587252096</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W40" t="n">
-        <v>9.680388587252096</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X40" t="n">
-        <v>9.680388587252096</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>79.19191919191917</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C41" t="n">
-        <v>79.19191919191917</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D41" t="n">
-        <v>43.60404040404041</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="E41" t="n">
-        <v>3.2</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="F41" t="n">
-        <v>3.2</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K41" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L41" t="n">
-        <v>82.40000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M41" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N41" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O41" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T41" t="n">
-        <v>160</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="U41" t="n">
-        <v>160</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="V41" t="n">
-        <v>119.5959595959596</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="W41" t="n">
-        <v>119.5959595959596</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="X41" t="n">
-        <v>119.5959595959596</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y41" t="n">
-        <v>79.19191919191917</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>38.78787878787876</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="C42" t="n">
-        <v>3.2</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K42" t="n">
-        <v>41.20000000000001</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L42" t="n">
-        <v>41.20000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M42" t="n">
-        <v>80.80000000000001</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="N42" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U42" t="n">
-        <v>119.5959595959596</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V42" t="n">
-        <v>79.19191919191917</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W42" t="n">
-        <v>79.19191919191917</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X42" t="n">
-        <v>38.78787878787876</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="Y42" t="n">
-        <v>38.78787878787876</v>
+        <v>26.7539638887914</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P43" t="n">
-        <v>130.8925097993733</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q43" t="n">
-        <v>90.48846939533291</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R43" t="n">
-        <v>50.0844289912925</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S43" t="n">
-        <v>9.680388587252096</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U43" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="V43" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="44">
@@ -9147,19 +9147,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7664149699872</v>
+        <v>252.3085620888997</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>246.8883803461852</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>245.2868411349413</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>247.775142874182</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,10 +9223,10 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>154.3835860932714</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>154.4281573182245</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -9238,10 +9238,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>150.5165545332427</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>156.523921204934</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,16 +9305,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>134.8846762812383</v>
+        <v>151.4268234001507</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>155.4679310665175</v>
       </c>
       <c r="N19" t="n">
-        <v>127.6855444652332</v>
+        <v>143.5593220035835</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>154.9986855707552</v>
       </c>
       <c r="P19" t="n">
         <v>135.0065633140411</v>
@@ -9381,22 +9381,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L20" t="n">
-        <v>274.1502533538256</v>
+        <v>278.1154692732874</v>
       </c>
       <c r="M20" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O20" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P20" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,16 +9460,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>178.5543797798742</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M21" t="n">
-        <v>180.5178723058567</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O21" t="n">
         <v>142.5962444444444</v>
@@ -9478,7 +9478,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9618,22 +9618,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L23" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N23" t="n">
-        <v>267.7969019804293</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>270.0982114216868</v>
+        <v>272.4472657249869</v>
       </c>
       <c r="P23" t="n">
-        <v>271.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>177.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N24" t="n">
-        <v>169.7255504671717</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O24" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>176.3234617176304</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M26" t="n">
-        <v>270.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O26" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
-        <v>269.6168341391079</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M27" t="n">
-        <v>182.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O27" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>172.3582457981686</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>260.0898510449805</v>
+        <v>262.4389053482807</v>
       </c>
       <c r="L29" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>268.7300716111111</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O29" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,19 +10174,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>176.9382181637126</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M30" t="n">
-        <v>182.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O30" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P30" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,19 +10329,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L32" t="n">
-        <v>274.1502533538256</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O32" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>182.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N33" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>179.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L35" t="n">
-        <v>275.7664149699872</v>
+        <v>278.1154692732874</v>
       </c>
       <c r="M35" t="n">
-        <v>268.7300716111111</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O35" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,22 +10645,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M36" t="n">
-        <v>182.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N36" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>180.9800828282828</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10806,16 +10806,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>275.7664149699872</v>
+        <v>278.1154692732874</v>
       </c>
       <c r="M38" t="n">
-        <v>270.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N38" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O38" t="n">
-        <v>268.4820498055251</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L39" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M39" t="n">
-        <v>180.5178723058567</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>173.9744074143302</v>
+        <v>176.3234617176304</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>260.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L41" t="n">
-        <v>275.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M41" t="n">
-        <v>268.7300716111111</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O41" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P41" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,19 +11119,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>176.2252773581974</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M42" t="n">
-        <v>182.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N42" t="n">
-        <v>171.3417120833333</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O42" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
@@ -11204,10 +11204,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M43" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23740,16 +23740,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>194.4497464039073</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>206.5537024452189</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>234.803505788924</v>
       </c>
       <c r="V17" t="n">
-        <v>327.7522584701349</v>
+        <v>311.2101113512225</v>
       </c>
       <c r="W17" t="n">
         <v>349.240968717413</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>83.61568703373068</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>155.1410239849254</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>183.6225815759092</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>211.3710588986367</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23850,10 +23850,10 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>167.2468210986278</v>
+        <v>150.7046739797154</v>
       </c>
       <c r="D19" t="n">
-        <v>148.6154730182124</v>
+        <v>134.0451498358743</v>
       </c>
       <c r="E19" t="n">
         <v>146.4339626465692</v>
@@ -23898,10 +23898,10 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>207.4744509180598</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9455894282815</v>
+        <v>211.403442309369</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>338.601669284252</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23935,16 +23935,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>304.2428021157672</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>330.8594832468445</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>342.105766276825</v>
       </c>
     </row>
     <row r="21">
@@ -24005,16 +24005,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>107.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>122.413080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
         <v>145.0692123933839</v>
@@ -24065,16 +24065,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>166.8110783456798</v>
       </c>
     </row>
     <row r="22">
@@ -24084,25 +24084,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
-        <v>108.6154730182124</v>
+        <v>104.4833006389838</v>
       </c>
       <c r="E22" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F22" t="n">
-        <v>136.2840225864452</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
         <v>167.9909793584588</v>
       </c>
       <c r="H22" t="n">
-        <v>162.2271725074396</v>
+        <v>161.4367220597573</v>
       </c>
       <c r="I22" t="n">
         <v>155.4504749272583</v>
@@ -24147,10 +24147,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24169,13 +24169,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>319.451041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
@@ -24184,7 +24184,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>170.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24223,16 +24223,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>347.366321224429</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>131.3011836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>107.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>100.9370400141553</v>
       </c>
       <c r="G24" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>68.10327185726787</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -24299,10 +24299,10 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>181.8092097017462</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>193.9289697178007</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
@@ -24324,19 +24324,19 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D25" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>146.4339626465692</v>
+        <v>145.6435121988869</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4210480229312</v>
+        <v>101.2888756437027</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>123.8588069792302</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24372,13 +24372,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>277.1820039200048</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="26">
@@ -24403,10 +24403,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>319.451041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
@@ -24457,19 +24457,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W26" t="n">
-        <v>309.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>330.8594832468445</v>
       </c>
       <c r="Y26" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,13 +24479,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>112.2130655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
         <v>157.6450804554009</v>
@@ -24527,10 +24527,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>61.28621672101858</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
@@ -24539,16 +24539,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>170.6949547454512</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C28" t="n">
         <v>167.2468210986278</v>
@@ -24573,13 +24573,13 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.9909793584588</v>
+        <v>123.8588069792302</v>
       </c>
       <c r="H28" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
-        <v>155.4504749272583</v>
+        <v>154.660024479576</v>
       </c>
       <c r="J28" t="n">
         <v>93.35918011667277</v>
@@ -24618,16 +24618,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>208.0054709445994</v>
       </c>
       <c r="W28" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>185.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y28" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="29">
@@ -24637,10 +24637,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>357.4925408780254</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
@@ -24649,10 +24649,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>362.7438733624829</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>371.1705651359065</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24697,16 +24697,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>288.8806410385104</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>346.2379386560536</v>
+        <v>342.105766276825</v>
       </c>
     </row>
     <row r="30">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>93.21134478398204</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>50.52501541979053</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -24770,19 +24770,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>160.1647286948216</v>
+        <v>156.032556315593</v>
       </c>
       <c r="U30" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X30" t="n">
-        <v>170.5409852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -24816,7 +24816,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -24840,10 +24840,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>77.02501781520832</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
@@ -24855,16 +24855,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
-        <v>212.137643323828</v>
+        <v>251.3471928761457</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X31" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="32">
@@ -24874,22 +24874,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>343.862224231856</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>329.4417408352278</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>371.1705651359065</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
@@ -24931,7 +24931,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>342.105766276825</v>
       </c>
     </row>
     <row r="33">
@@ -24953,13 +24953,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>131.3011836498674</v>
+        <v>122.4010112706387</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>103.3128931854102</v>
       </c>
       <c r="E33" t="n">
         <v>157.6450804554009</v>
@@ -24974,10 +24974,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>51.27160674604839</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25016,13 +25016,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25050,16 +25050,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>69.21308724117605</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25074,7 +25074,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
         <v>86.16204325169439</v>
@@ -25086,13 +25086,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>183.8134170490529</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3190293564909</v>
+        <v>242.1868569772623</v>
       </c>
       <c r="V34" t="n">
-        <v>252.137643323828</v>
+        <v>251.3471928761457</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
@@ -25101,7 +25101,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="35">
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>347.5018416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>310.5938838986874</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X35" t="n">
-        <v>329.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y35" t="n">
-        <v>346.2379386560536</v>
+        <v>342.105766276825</v>
       </c>
     </row>
     <row r="36">
@@ -25193,19 +25193,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>112.2130655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>100.9370400141553</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>99.21849105784395</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25244,7 +25244,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>156.032556315593</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -25256,10 +25256,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -25269,13 +25269,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D37" t="n">
-        <v>139.4784475817263</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
         <v>146.4339626465692</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>86.16204325169439</v>
@@ -25323,13 +25323,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>227.9455894282815</v>
+        <v>185.7444073364771</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3190293564909</v>
+        <v>242.1868569772623</v>
       </c>
       <c r="V37" t="n">
-        <v>252.137643323828</v>
+        <v>208.0054709445994</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25338,7 +25338,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="38">
@@ -25348,13 +25348,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>342.7338416634806</v>
+        <v>338.601669284252</v>
       </c>
       <c r="C38" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>314.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25363,7 +25363,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>371.1705651359065</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25399,7 +25399,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>170.1484521546208</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25414,10 +25414,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y38" t="n">
-        <v>351.0059386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25430,7 +25430,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>64.92583415264315</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>161.2931112631971</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>181.8092097017462</v>
       </c>
       <c r="V39" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>165.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="40">
@@ -25509,10 +25509,10 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>123.1146487193992</v>
       </c>
       <c r="D40" t="n">
-        <v>148.6154730182124</v>
+        <v>104.4833006389838</v>
       </c>
       <c r="E40" t="n">
         <v>146.4339626465692</v>
@@ -25533,7 +25533,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K40" t="n">
-        <v>22.26949182588285</v>
+        <v>21.47904137820059</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25548,34 +25548,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>212.1690686507152</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="41">
@@ -25591,16 +25591,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>319.451041620683</v>
+        <v>327.0930163603668</v>
       </c>
       <c r="E41" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25639,22 +25639,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>208.7852545293897</v>
       </c>
       <c r="U41" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>369.731100678469</v>
+        <v>342.1410754181529</v>
       </c>
       <c r="Y41" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25667,7 +25667,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>137.4764989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
@@ -25679,7 +25679,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>113.0422229139242</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -25721,19 +25721,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>224.1049579006035</v>
       </c>
       <c r="X42" t="n">
-        <v>165.7729852034775</v>
+        <v>178.1829599431613</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>178.0926705169882</v>
       </c>
     </row>
     <row r="43">
@@ -25785,34 +25785,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>221.5300047269019</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
-        <v>252.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>258.9329730762748</v>
       </c>
       <c r="X43" t="n">
-        <v>225.7096553890372</v>
+        <v>198.119630128721</v>
       </c>
       <c r="Y43" t="n">
-        <v>218.5846533520948</v>
+        <v>196.1358939915854</v>
       </c>
     </row>
     <row r="44">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333272.9571474838</v>
+        <v>347810.2001794757</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367453.5983135027</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367453.5983135024</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367453.5983135024</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367453.5983135026</v>
+        <v>357450.1188230734</v>
       </c>
     </row>
     <row r="16">
@@ -26264,46 +26264,46 @@
         <v>53753.7027657232</v>
       </c>
       <c r="C2" t="n">
-        <v>53753.70276572322</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="D2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="E2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="F2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="G2" t="n">
-        <v>53753.70276572321</v>
+        <v>56096.88467139944</v>
       </c>
       <c r="H2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="I2" t="n">
-        <v>59263.10091834212</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="J2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="K2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559939</v>
       </c>
       <c r="L2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="M2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559938</v>
       </c>
       <c r="N2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="O2" t="n">
-        <v>59263.10091834213</v>
+        <v>57650.69256249411</v>
       </c>
       <c r="P2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
     </row>
     <row r="3">
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4533.95439308712</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>7444.037125460638</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="D4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="E4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="F4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="G4" t="n">
-        <v>10750.74055314464</v>
+        <v>8786.916540968321</v>
       </c>
       <c r="H4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="I4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="J4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="K4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="L4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265167</v>
       </c>
       <c r="M4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="N4" t="n">
-        <v>11908.72037095864</v>
+        <v>9396.056446265166</v>
       </c>
       <c r="O4" t="n">
-        <v>11908.72037095864</v>
+        <v>9044.140630683767</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
     </row>
     <row r="5">
@@ -26432,31 +26432,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1005.762544829877</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578562</v>
+        <v>11727.08670857896</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.362212578577</v>
+        <v>11727.08670857896</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.36221257857</v>
+        <v>11727.08670857895</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257857</v>
+        <v>45354.68670857896</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257857</v>
+        <v>45354.68670857895</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257857</v>
+        <v>41770.25119251412</v>
       </c>
       <c r="H6" t="n">
-        <v>34130.02054738349</v>
+        <v>40253.17302321647</v>
       </c>
       <c r="I6" t="n">
-        <v>44922.38054738348</v>
+        <v>47697.21014867711</v>
       </c>
       <c r="J6" t="n">
-        <v>44922.38054738349</v>
+        <v>47697.21014867711</v>
       </c>
       <c r="K6" t="n">
-        <v>44922.38054738349</v>
+        <v>47697.21014867712</v>
       </c>
       <c r="L6" t="n">
-        <v>44922.38054738349</v>
+        <v>47697.21014867711</v>
       </c>
       <c r="M6" t="n">
-        <v>44922.38054738349</v>
+        <v>47697.21014867711</v>
       </c>
       <c r="N6" t="n">
-        <v>44922.38054738349</v>
+        <v>47697.21014867711</v>
       </c>
       <c r="O6" t="n">
-        <v>44922.38054738349</v>
+        <v>46929.07839598312</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257857</v>
+        <v>45354.68670857895</v>
       </c>
     </row>
   </sheetData>
@@ -26742,31 +26742,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26959,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
   </sheetData>
@@ -35802,19 +35802,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>15.87377753835033</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,10 +35878,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>15.87377753835032</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -35893,10 +35893,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35960,16 +35960,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>15.87377753835033</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>16.54214711891245</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -36036,22 +36036,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L20" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,16 +36115,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M21" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -36133,7 +36133,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36273,22 +36273,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N23" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N24" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,22 +36510,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M27" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36747,22 +36747,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,19 +36829,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,19 +36984,19 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L32" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="O32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="N33" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M35" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,22 +37300,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M36" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37461,16 +37461,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O38" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M39" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M41" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,19 +37774,19 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M42" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N42" t="n">
-        <v>40</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -37859,10 +37859,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M43" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
